--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.19546734677386</v>
+        <v>4.419263443850753</v>
       </c>
       <c r="D2" t="n">
-        <v>26.09156667680626</v>
+        <v>4.239879584981018</v>
       </c>
       <c r="E2" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F2" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.14959780767239</v>
+        <v>4.411809643746763</v>
       </c>
       <c r="D3" t="n">
-        <v>27.49137644686144</v>
+        <v>4.467348672614984</v>
       </c>
       <c r="E3" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F3" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.45861554789654</v>
+        <v>7.387025026533188</v>
       </c>
       <c r="D4" t="n">
-        <v>46.70946325288461</v>
+        <v>7.590287778593749</v>
       </c>
       <c r="E4" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F4" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.03103723246959</v>
+        <v>6.830043550276308</v>
       </c>
       <c r="D5" t="n">
-        <v>41.73307059928329</v>
+        <v>6.781623972383535</v>
       </c>
       <c r="E5" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F5" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.28305523590856</v>
+        <v>3.783496475835141</v>
       </c>
       <c r="D6" t="n">
-        <v>22.95518721609479</v>
+        <v>3.730217922615403</v>
       </c>
       <c r="E6" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F6" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.39005882760433</v>
+        <v>4.613384559485703</v>
       </c>
       <c r="D7" t="n">
-        <v>28.027612203482</v>
+        <v>4.554486983065826</v>
       </c>
       <c r="E7" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F7" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.1090104975967</v>
+        <v>5.055214205859464</v>
       </c>
       <c r="D8" t="n">
-        <v>64.83135916638869</v>
+        <v>10.53509586453816</v>
       </c>
       <c r="E8" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F8" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17058454375663</v>
+        <v>5.065219988360452</v>
       </c>
       <c r="D9" t="n">
-        <v>30.30312197986915</v>
+        <v>4.924257321728737</v>
       </c>
       <c r="E9" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F9" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.75282826120477</v>
+        <v>4.022334592445775</v>
       </c>
       <c r="D10" t="n">
-        <v>24.9197124982109</v>
+        <v>4.049453280959272</v>
       </c>
       <c r="E10" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F10" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.49961597947654</v>
+        <v>6.743687596664937</v>
       </c>
       <c r="D11" t="n">
-        <v>59.17633690082585</v>
+        <v>9.616154746384201</v>
       </c>
       <c r="E11" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F11" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.49371192784569</v>
+        <v>5.280228188274926</v>
       </c>
       <c r="D12" t="n">
-        <v>49.35912336359132</v>
+        <v>8.020857546583589</v>
       </c>
       <c r="E12" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F12" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.709680929572</v>
+        <v>1.57782315105545</v>
       </c>
       <c r="D13" t="n">
-        <v>10.71853527911909</v>
+        <v>1.741761982856852</v>
       </c>
       <c r="E13" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F13" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.53742163435576</v>
+        <v>6.749831015582811</v>
       </c>
       <c r="D14" t="n">
-        <v>40.54530728290204</v>
+        <v>6.588612433471583</v>
       </c>
       <c r="E14" t="n">
-        <v>9.371231938060653</v>
+        <v>1.522825189934856</v>
       </c>
       <c r="F14" t="n">
-        <v>14.96646976663019</v>
+        <v>2.432051337077407</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
